--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -12253,14 +12253,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -12283,15 +12284,20 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
+          <t>חבילת אחריות</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
           <t>חניכים (מחושב מגיליון «חניכים»)</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>ערכת צבע</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>מס' חניכים</t>
         </is>
@@ -12303,21 +12309,22 @@
           <t>קבוצה 1</t>
         </is>
       </c>
-      <c r="B3" s="86" t="inlineStr">
+      <c r="B3" s="86" t="n"/>
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>ארוחות שבת</t>
         </is>
       </c>
-      <c r="C3" s="87">
+      <c r="D3" s="87">
         <f>IF($A3="","",'חניכים'!$F$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>ורוד</t>
         </is>
       </c>
-      <c r="E3" s="88">
+      <c r="F3" s="88">
         <f>IF($A3="","",COUNTIF('חניכים'!$B$3:$B$132,$A3))</f>
         <v/>
       </c>
@@ -12328,21 +12335,22 @@
           <t>קבוצה 2</t>
         </is>
       </c>
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="86" t="n"/>
+      <c r="C4" s="69" t="inlineStr">
         <is>
           <t>ארוחות שישי וסעודה שלישית</t>
         </is>
       </c>
-      <c r="C4" s="87">
+      <c r="D4" s="87">
         <f>IF($A4="","",'חניכים'!$G$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>ים</t>
         </is>
       </c>
-      <c r="E4" s="88">
+      <c r="F4" s="88">
         <f>IF($A4="","",COUNTIF('חניכים'!$B$3:$B$132,$A4))</f>
         <v/>
       </c>
@@ -12353,21 +12361,22 @@
           <t>קבוצה 3</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="69" t="inlineStr">
         <is>
           <t>טיש ואחריות טכנית</t>
         </is>
       </c>
-      <c r="C5" s="87">
+      <c r="D5" s="87">
         <f>IF($A5="","",'חניכים'!$H$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>ספארי</t>
         </is>
       </c>
-      <c r="E5" s="88">
+      <c r="F5" s="88">
         <f>IF($A5="","",COUNTIF('חניכים'!$B$3:$B$132,$A5))</f>
         <v/>
       </c>
@@ -12378,21 +12387,22 @@
           <t>קבוצה 4</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="86" t="n"/>
+      <c r="C6" s="69" t="inlineStr">
         <is>
           <t>קידוש ומאפים</t>
         </is>
       </c>
-      <c r="C6" s="87">
+      <c r="D6" s="87">
         <f>IF($A6="","",'חניכים'!$I$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>שדה</t>
         </is>
       </c>
-      <c r="E6" s="88">
+      <c r="F6" s="88">
         <f>IF($A6="","",COUNTIF('חניכים'!$B$3:$B$132,$A6))</f>
         <v/>
       </c>
@@ -12400,16 +12410,17 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="80" t="n"/>
       <c r="B7" s="86" t="n"/>
-      <c r="C7" s="87">
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="87">
         <f>IF($A7="","",'חניכים'!$J$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>סגול</t>
         </is>
       </c>
-      <c r="E7" s="88">
+      <c r="F7" s="88">
         <f>IF($A7="","",COUNTIF('חניכים'!$B$3:$B$132,$A7))</f>
         <v/>
       </c>
@@ -12417,16 +12428,17 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="80" t="n"/>
       <c r="B8" s="86" t="n"/>
-      <c r="C8" s="87">
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="87">
         <f>IF($A8="","",'חניכים'!$K$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D8" s="69" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>ירוק</t>
         </is>
       </c>
-      <c r="E8" s="88">
+      <c r="F8" s="88">
         <f>IF($A8="","",COUNTIF('חניכים'!$B$3:$B$132,$A8))</f>
         <v/>
       </c>
@@ -12434,17 +12446,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>שמות הקבוצות והמובילים נקבעים כאן. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
+          <t>שמות הקבוצות והמובילים נקבעים כאן. «חבילת אחריות» היא תחום האחריות של הקבוצה בשבת הזו. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ורוד,ים,ספארי,שדה,סגול,ירוק"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22809,7 +22821,7 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="26">
-        <f>IF('קבוצות'!$C$3="","",'קבוצות'!$C$3)</f>
+        <f>IF('קבוצות'!$D$3="","",'קבוצות'!$D$3)</f>
         <v/>
       </c>
     </row>
@@ -23635,7 +23647,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="37">
-        <f>IF('קבוצות'!$C$4="","",'קבוצות'!$C$4)</f>
+        <f>IF('קבוצות'!$D$4="","",'קבוצות'!$D$4)</f>
         <v/>
       </c>
     </row>
@@ -24461,7 +24473,7 @@
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="41">
-        <f>IF('קבוצות'!$C$5="","",'קבוצות'!$C$5)</f>
+        <f>IF('קבוצות'!$D$5="","",'קבוצות'!$D$5)</f>
         <v/>
       </c>
     </row>
@@ -25287,7 +25299,7 @@
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="45">
-        <f>IF('קבוצות'!$C$6="","",'קבוצות'!$C$6)</f>
+        <f>IF('קבוצות'!$D$6="","",'קבוצות'!$D$6)</f>
         <v/>
       </c>
     </row>
@@ -26113,7 +26125,7 @@
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="49">
-        <f>IF('קבוצות'!$C$7="","",'קבוצות'!$C$7)</f>
+        <f>IF('קבוצות'!$D$7="","",'קבוצות'!$D$7)</f>
         <v/>
       </c>
     </row>
@@ -26939,7 +26951,7 @@
     </row>
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="53">
-        <f>IF('קבוצות'!$C$8="","",'קבוצות'!$C$8)</f>
+        <f>IF('קבוצות'!$D$8="","",'קבוצות'!$D$8)</f>
         <v/>
       </c>
     </row>
@@ -27900,362 +27912,362 @@
   </mergeCells>
   <conditionalFormatting sqref="A2:F3">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="13" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A22">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:F1">
     <cfRule type="expression" priority="3" dxfId="7">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="8">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="9">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="10">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="11">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="12">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F28">
     <cfRule type="expression" priority="19" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="22" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="25" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="28" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="31" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="34" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:A47">
     <cfRule type="expression" priority="20" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="26" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="32" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="35" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:F26">
     <cfRule type="expression" priority="21" dxfId="7">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="24" dxfId="8">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" dxfId="9">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="10">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="33" dxfId="11">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="36" dxfId="12">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:F53">
     <cfRule type="expression" priority="37" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="40" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="43" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="46" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="49" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="52" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:A72">
     <cfRule type="expression" priority="38" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="41" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="44" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="47" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="50" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="53" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
     <cfRule type="expression" priority="39" dxfId="7">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="42" dxfId="8">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="45" dxfId="9">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="48" dxfId="10">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="51" dxfId="11">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="54" dxfId="12">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:F78">
     <cfRule type="expression" priority="55" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="58" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="61" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="64" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="67" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="70" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80:A97">
     <cfRule type="expression" priority="56" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="59" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="62" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="65" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="68" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="71" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
     <cfRule type="expression" priority="57" dxfId="7">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="60" dxfId="8">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="63" dxfId="9">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="66" dxfId="10">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="69" dxfId="11">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="72" dxfId="12">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:F103">
     <cfRule type="expression" priority="73" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="76" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="79" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="82" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="85" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="88" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:A122">
     <cfRule type="expression" priority="74" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="77" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="80" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="83" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="86" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="89" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101:F101">
     <cfRule type="expression" priority="75" dxfId="7">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="78" dxfId="8">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="81" dxfId="9">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="84" dxfId="10">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="87" dxfId="11">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="90" dxfId="12">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127:F128">
     <cfRule type="expression" priority="91" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="94" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="97" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="100" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="103" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="106" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A130:A147">
     <cfRule type="expression" priority="92" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="95" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="98" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="101" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="104" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="107" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:F126">
     <cfRule type="expression" priority="93" dxfId="7">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="96" dxfId="8">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="99" dxfId="9">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="102" dxfId="10">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="105" dxfId="11">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="108" dxfId="12">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
